--- a/sample_data/crm_contacts.xlsx
+++ b/sample_data/crm_contacts.xlsx
@@ -2536,7 +2536,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>+91 98765 43210</t>
+          <t>+91 90000 12345</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
